--- a/downloads/droits-reutilisation.xlsx
+++ b/downloads/droits-reutilisation.xlsx
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4">

--- a/downloads/droits-reutilisation.xlsx
+++ b/downloads/droits-reutilisation.xlsx
@@ -457,10 +457,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
